--- a/ranked mapping difference.xlsx
+++ b/ranked mapping difference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipsafr-my.sharepoint.com/personal/pierre_gueno_ipsa_fr/Documents/Documents/IPSA/Aero 4/Stage A4/BIRA IASB Bruxelles/code/git-internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9188D0E6-1E70-491D-83AE-337486BCA453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{9188D0E6-1E70-491D-83AE-337486BCA453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B00FF4A-179E-444F-9986-D83E38F15BE2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{A86ECA96-17A7-45EB-9152-42653F182B1F}"/>
   </bookViews>
@@ -551,16 +551,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -910,9 +909,7 @@
   <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="8.88671875" style="4"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -921,19 +918,19 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <f>1</f>
         <v>1</v>
       </c>
@@ -942,13 +939,13 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <f>1+F3</f>
         <v>2</v>
       </c>
@@ -957,13 +954,13 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <f t="shared" ref="F5:F41" si="0">1+F4</f>
         <v>3</v>
       </c>
@@ -972,13 +969,13 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -987,13 +984,13 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1002,13 +999,13 @@
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1017,13 +1014,13 @@
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1032,13 +1029,13 @@
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1047,13 +1044,13 @@
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1062,13 +1059,13 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1077,13 +1074,13 @@
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1092,13 +1089,13 @@
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1107,13 +1104,13 @@
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1122,13 +1119,13 @@
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1137,13 +1134,13 @@
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1152,13 +1149,13 @@
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1167,13 +1164,13 @@
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1182,13 +1179,13 @@
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1197,13 +1194,13 @@
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1212,13 +1209,13 @@
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1227,13 +1224,13 @@
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1242,13 +1239,13 @@
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -1257,13 +1254,13 @@
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -1272,13 +1269,13 @@
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -1287,13 +1284,13 @@
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -1302,13 +1299,13 @@
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -1317,13 +1314,13 @@
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -1332,13 +1329,13 @@
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -1347,13 +1344,13 @@
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>96</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -1362,13 +1359,13 @@
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1377,13 +1374,13 @@
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -1392,13 +1389,13 @@
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>102</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -1407,13 +1404,13 @@
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -1422,13 +1419,13 @@
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" t="s">
         <v>106</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -1437,13 +1434,13 @@
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -1452,13 +1449,13 @@
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" t="s">
         <v>110</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -1467,13 +1464,13 @@
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -1482,13 +1479,13 @@
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -1497,25 +1494,25 @@
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
+      <c r="A42" s="2"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
+      <c r="A44" s="2"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
+      <c r="A46" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1524,36 +1521,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BA3CF9-564F-4D89-B49E-6CCBCA01F18E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="5"/>
-    <col min="2" max="2" width="18.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="2" max="2" width="18.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>11</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>38</v>
       </c>
       <c r="D2">
@@ -1562,13 +1562,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>3</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>39</v>
       </c>
       <c r="D3">
@@ -1577,13 +1577,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>32</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>22</v>
       </c>
       <c r="D4">
@@ -1592,13 +1592,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>28</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>29</v>
       </c>
       <c r="D5">
@@ -1607,13 +1607,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>33</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>23</v>
       </c>
       <c r="D6">
@@ -1622,13 +1622,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>34</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <f>2</f>
         <v>2</v>
       </c>
@@ -1638,13 +1638,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>19</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>14</v>
       </c>
       <c r="D8">
@@ -1653,13 +1653,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>35</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>33</v>
       </c>
       <c r="D9">
@@ -1668,13 +1668,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>12</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>32</v>
       </c>
       <c r="D10">
@@ -1683,13 +1683,13 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>36</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>17</v>
       </c>
       <c r="D11">
@@ -1698,13 +1698,13 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>13</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>30</v>
       </c>
       <c r="D12">
@@ -1713,13 +1713,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>6</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>31</v>
       </c>
       <c r="D13">
@@ -1728,13 +1728,13 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>6</v>
       </c>
       <c r="D14">
@@ -1743,13 +1743,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>21</v>
       </c>
       <c r="D15">
@@ -1758,13 +1758,13 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>25</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>3</v>
       </c>
       <c r="D16">
@@ -1773,13 +1773,13 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>31</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>8</v>
       </c>
       <c r="D17">
@@ -1788,13 +1788,13 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>26</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>10</v>
       </c>
       <c r="D18">
@@ -1803,13 +1803,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>22</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <f>1</f>
         <v>1</v>
       </c>
@@ -1819,13 +1819,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>37</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>24</v>
       </c>
       <c r="D20">
@@ -1834,13 +1834,13 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>15</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>34</v>
       </c>
       <c r="D21">
@@ -1849,13 +1849,13 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>29</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>19</v>
       </c>
       <c r="D22">
@@ -1864,13 +1864,13 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>18</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>20</v>
       </c>
       <c r="D23">
@@ -1879,13 +1879,13 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>5</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>28</v>
       </c>
       <c r="D24">
@@ -1894,13 +1894,13 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>38</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>7</v>
       </c>
       <c r="D25">
@@ -1909,13 +1909,13 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>27</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>11</v>
       </c>
       <c r="D26">
@@ -1924,13 +1924,13 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>23</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>5</v>
       </c>
       <c r="D27">
@@ -1939,13 +1939,13 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>21</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>13</v>
       </c>
       <c r="D28">
@@ -1954,13 +1954,13 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>14</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <v>12</v>
       </c>
       <c r="D29">
@@ -1969,13 +1969,13 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>9</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>26</v>
       </c>
       <c r="D30">
@@ -1984,13 +1984,13 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>2</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="4">
         <v>18</v>
       </c>
       <c r="D31">
@@ -1999,13 +1999,13 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>39</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="4">
         <v>9</v>
       </c>
       <c r="D32">
@@ -2014,13 +2014,13 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>30</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="4">
         <v>4</v>
       </c>
       <c r="D33">
@@ -2029,13 +2029,13 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>7</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34">
@@ -2044,13 +2044,13 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>4</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="4">
         <v>15</v>
       </c>
       <c r="D35">
@@ -2059,13 +2059,13 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>17</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="4">
         <v>36</v>
       </c>
       <c r="D36">
@@ -2074,13 +2074,13 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="4">
         <v>27</v>
       </c>
       <c r="D37">
@@ -2089,13 +2089,13 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="4">
         <v>16</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="4">
         <v>25</v>
       </c>
       <c r="D38">
@@ -2104,13 +2104,13 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>1</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="4">
         <v>37</v>
       </c>
       <c r="D39">
@@ -2119,13 +2119,13 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>20</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="4">
         <v>35</v>
       </c>
       <c r="D40">
@@ -2150,5 +2150,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>